--- a/Sergio i Dome/Informe pràctica C.xlsx
+++ b/Sergio i Dome/Informe pràctica C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergio/Desktop/University/5nto/LACE/LACE/Sergio i Dome/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4E7BC5-C1E2-DC47-BCD4-F5E5DEE41B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA734BD7-726C-F643-8F9E-6F06C037694C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="840" windowWidth="34200" windowHeight="21400" activeTab="1" xr2:uid="{C1122783-245A-4FED-BDEB-F09B1698DCDF}"/>
   </bookViews>
@@ -17,9 +17,6 @@
     <sheet name="C2" sheetId="4" r:id="rId2"/>
     <sheet name="Càlculs" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'C1'!$A$1:$I$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'C2'!$A$1:$I$4</definedName>
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -351,7 +348,7 @@
     <numFmt numFmtId="165" formatCode="0.0000000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
-    <numFmt numFmtId="169" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="0.00000"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -647,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -683,6 +680,98 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -694,108 +783,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -849,11 +836,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="es-ES_tradnl"/>
-              <a:t>Calibratge Abs. vs. Conc.</a:t>
+              <a:t>Calibratge per</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="es-ES_tradnl" baseline="0"/>
-              <a:t> Patró Fe(II)}</a:t>
+              <a:t> patrons externs</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1863,8 +1850,8 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>23708</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="CuadroTexto 2">
@@ -3148,7 +3135,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="CuadroTexto 2">
@@ -3606,8 +3593,8 @@
       <xdr:row>58</xdr:row>
       <xdr:rowOff>37165</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CuadroTexto 4">
@@ -4090,7 +4077,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CuadroTexto 4">
@@ -6019,65 +6006,165 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="C1"/>
-      <sheetName val="C2"/>
-      <sheetName val="Càlculs"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="74">
-          <cell r="K74">
-            <v>8.0140000000000018E-4</v>
-          </cell>
-          <cell r="L74">
-            <v>0.159</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="K75">
-            <v>1.6028000000000004E-3</v>
-          </cell>
-          <cell r="L75">
-            <v>0.32200000000000001</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="K76">
-            <v>2.4042000000000004E-3</v>
-          </cell>
-          <cell r="L76">
-            <v>0.47</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="K77">
-            <v>3.2056000000000007E-3</v>
-          </cell>
-          <cell r="L77">
-            <v>0.62</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="K78">
-            <v>4.0070000000000001E-3</v>
-          </cell>
-          <cell r="L78">
-            <v>0.77300000000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>45358</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>199573</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>2866572</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9574FEFB-99DF-EAA6-A852-C5B757BAB2F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="45358" y="1052286"/>
+          <a:ext cx="6449786" cy="3410857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Per a la detecció de la </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>concentració de ferro i manganés en un comprimit multivitamínic</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>utilitzem el model 55 AA de la marca Agilent, que permet quantificar la mostra mitjançant espectroscòpia d’absorció atòmica.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-GB" b="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Com a font de llum, s’empra una làmpada de càtode buit multielemental. Aquesta làmpada emet a longituds d’ona molt específiques; concretament, ens fixem en l’emissió a 248,3 nm per</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0" baseline="0"/>
+            <a:t> la quantificació del</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t> ferro i 279,5 nm per la quantificació del manganés. Aquestes longitud d’ona és absorbida pels àtoms de ferro</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0" baseline="0"/>
+            <a:t> i manganés </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>presents en la mostra, els quals s’exciten. Així, podem determinar la concentració de coure mitjançant la diferència d’intensitat entre una mostra sense ferro</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0" baseline="0"/>
+            <a:t> i manganés</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t> (el blanc) i la</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0" baseline="0"/>
+            <a:t> dissolució que conté el comprimit multivitamínic</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-GB" b="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Després de realitzar un calibratge amb solucions patró de concentració coneguda de ferro i manganés, i mitjançant la llei de Lambert-Beer, podem quantificar la concentració de de ferro i manganés a partir d’una recta de regressió.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-GB" b="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Nota: És essencial mantenir l’equip net i lliure de residus, ja que, en tractar-se d’una tècnica de quantificació atòmica, la presència d’interferències pot provocar desviacions significatives en els resultats.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6383,210 +6470,209 @@
   <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" style="22" customWidth="1"/>
-    <col min="2" max="2" width="25.5" style="22" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="22" customWidth="1"/>
-    <col min="4" max="7" width="12.6640625" style="22" customWidth="1"/>
-    <col min="8" max="8" width="22" style="22" customWidth="1"/>
-    <col min="9" max="9" width="15" style="22" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="22"/>
-    <col min="11" max="11" width="13.83203125" style="22" customWidth="1"/>
-    <col min="12" max="16384" width="11.5" style="22"/>
+    <col min="1" max="1" width="16.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
+    <col min="4" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="1"/>
+    <col min="11" max="11" width="13.83203125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="39">
+      <c r="F1" s="25">
         <v>45792</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="21" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="26" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
       <c r="E3"/>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="23"/>
+      <c r="A4" s="2"/>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="65" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="7" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-    </row>
-    <row r="8" spans="1:20" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-    </row>
-    <row r="9" spans="1:20" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="23" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+    </row>
+    <row r="8" spans="1:20" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+    </row>
+    <row r="9" spans="1:20" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="22"/>
+      <c r="F9" s="1"/>
       <c r="H9" s="1">
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J9" s="22"/>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="1">
         <v>12393</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="1">
         <v>144</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="23"/>
+      <c r="A14" s="2"/>
     </row>
     <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="23"/>
+      <c r="A16" s="2"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="23"/>
-      <c r="H17" s="22" t="s">
+      <c r="A17" s="2"/>
+      <c r="H17" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H18" s="42" t="s">
+      <c r="H18" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="I18" s="42">
+      <c r="I18" s="27">
         <v>392.14</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="I19" s="42">
+      <c r="I19" s="27">
         <v>55.844999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="H21" s="22" t="s">
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="H21" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J22" s="44">
+      <c r="J22" s="29">
         <f>E13*I19/I18</f>
         <v>20.507165808129752</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H23" s="43" t="s">
+      <c r="H23" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="19">
         <f>J22/500</f>
         <v>4.1014331616259503E-2</v>
       </c>
@@ -6598,163 +6684,163 @@
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="27">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="18">
         <f>J23*25/50</f>
         <v>2.0507165808129751E-2</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="1">
         <f>5*10^(-3)/100</f>
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="23"/>
+      <c r="A34" s="2"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F36" s="22" t="s">
+      <c r="F36" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="59" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="40" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C40" s="54" t="s">
+      <c r="C40" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D40" s="54" t="s">
+      <c r="D40" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="54" t="s">
+      <c r="E40" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="54" t="s">
+      <c r="F40" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="M40" s="45"/>
+      <c r="M40" s="30"/>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C41" s="62">
+      <c r="C41" s="43">
         <v>1</v>
       </c>
-      <c r="D41" s="63">
+      <c r="D41" s="44">
         <v>1</v>
       </c>
-      <c r="E41" s="64">
+      <c r="E41" s="45">
         <f>C41*$F$30/25</f>
         <v>8.2028663232519008E-4</v>
       </c>
-      <c r="F41" s="65">
+      <c r="F41" s="46">
         <v>0.156</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C42" s="62">
+      <c r="C42" s="43">
         <v>2</v>
       </c>
-      <c r="D42" s="63">
+      <c r="D42" s="44">
         <v>1</v>
       </c>
-      <c r="E42" s="66">
+      <c r="E42" s="47">
         <f>$F$30*C42/25</f>
         <v>1.6405732646503802E-3</v>
       </c>
-      <c r="F42" s="65">
+      <c r="F42" s="46">
         <v>0.33100000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C43" s="62">
+      <c r="C43" s="43">
         <v>3</v>
       </c>
-      <c r="D43" s="63">
+      <c r="D43" s="44">
         <v>1</v>
       </c>
-      <c r="E43" s="66">
+      <c r="E43" s="47">
         <f>$F$30*C43/25</f>
         <v>2.4608598969755703E-3</v>
       </c>
-      <c r="F43" s="65">
+      <c r="F43" s="46">
         <v>0.496</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C44" s="62">
+      <c r="C44" s="43">
         <v>4</v>
       </c>
-      <c r="D44" s="63">
+      <c r="D44" s="44">
         <v>1</v>
       </c>
-      <c r="E44" s="66">
+      <c r="E44" s="47">
         <f>$F$30*C44/25</f>
         <v>3.2811465293007603E-3</v>
       </c>
-      <c r="F44" s="65">
+      <c r="F44" s="46">
         <v>0.67500000000000004</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C45" s="62">
+      <c r="C45" s="43">
         <v>5</v>
       </c>
-      <c r="D45" s="63">
+      <c r="D45" s="44">
         <v>1</v>
       </c>
-      <c r="E45" s="66">
+      <c r="E45" s="47">
         <f>$F$30*C45/25</f>
         <v>4.1014331616259503E-3</v>
       </c>
-      <c r="F45" s="65">
+      <c r="F45" s="46">
         <v>0.86799999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="47" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="23"/>
+      <c r="A49" s="2"/>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -6764,151 +6850,151 @@
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="25">
+      <c r="E62" s="16">
         <f>25*E43/(F33*10^3)</f>
         <v>1.2304299484877852</v>
       </c>
-      <c r="F62" s="22" t="s">
+      <c r="F62" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="46">
+      <c r="E64" s="31">
         <v>1</v>
       </c>
-      <c r="F64" s="22" t="s">
+      <c r="F64" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E65" s="46"/>
+      <c r="E65" s="31"/>
     </row>
     <row r="66" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="23" t="s">
+      <c r="A66" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E66" s="46">
+      <c r="E66" s="31">
         <v>2.3E-2</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E67" s="46"/>
+      <c r="E67" s="31"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="23" t="s">
+      <c r="A68" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E68" s="46">
+      <c r="E68" s="31">
         <v>0.45600000000000002</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E69" s="46"/>
+      <c r="E69" s="31"/>
     </row>
     <row r="70" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B70" s="23"/>
-      <c r="E70" s="46">
+      <c r="B70" s="2"/>
+      <c r="E70" s="31">
         <f>E68-E66</f>
         <v>0.433</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="72" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="23" t="s">
+      <c r="A72" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H73" s="55" t="s">
+      <c r="H73" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="I73" s="56"/>
-      <c r="J73" s="56"/>
-      <c r="K73" s="57"/>
+      <c r="I73" s="50"/>
+      <c r="J73" s="50"/>
+      <c r="K73" s="51"/>
     </row>
     <row r="74" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H74" s="47" t="s">
+      <c r="H74" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="I74" s="48" cm="1">
+      <c r="I74" s="33" cm="1">
         <f t="array" ref="I74:J78">LINEST(F41:F45,E41:E45,1,1)</f>
         <v>215.53441569423305</v>
       </c>
-      <c r="J74" s="49">
+      <c r="J74" s="34">
         <v>-2.5200000000000111E-2</v>
       </c>
-      <c r="K74" s="50" t="s">
+      <c r="K74" s="35" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H75" s="47" t="s">
+      <c r="H75" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="I75" s="48">
+      <c r="I75" s="33">
         <v>3.4795600765272168</v>
       </c>
-      <c r="J75" s="49">
+      <c r="J75" s="34">
         <v>9.4664319219721679E-3</v>
       </c>
-      <c r="K75" s="50" t="s">
+      <c r="K75" s="35" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H76" s="47" t="s">
+      <c r="H76" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="I76" s="49">
+      <c r="I76" s="34">
         <v>0.99921873701358077</v>
       </c>
-      <c r="J76" s="49">
+      <c r="J76" s="34">
         <v>9.0258886912407098E-3</v>
       </c>
-      <c r="K76" s="50" t="s">
+      <c r="K76" s="35" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H77" s="47" t="s">
+      <c r="H77" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="I77" s="48">
+      <c r="I77" s="33">
         <v>3836.936170212753</v>
       </c>
-      <c r="J77" s="50">
+      <c r="J77" s="35">
         <v>3</v>
       </c>
-      <c r="K77" s="50" t="s">
+      <c r="K77" s="35" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H78" s="47" t="s">
+      <c r="H78" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="I78" s="51">
+      <c r="I78" s="36">
         <v>0.31258240000000004</v>
       </c>
-      <c r="J78" s="52">
+      <c r="J78" s="37">
         <v>2.4440000000000084E-4</v>
       </c>
-      <c r="K78" s="50" t="s">
+      <c r="K78" s="35" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6922,374 +7008,374 @@
     <row r="86" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="87" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="88" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="23" t="s">
+      <c r="A88" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G88" s="27">
+      <c r="G88" s="18">
         <f>(E70-J74)/I74</f>
         <v>2.1258785912409623E-3</v>
       </c>
-      <c r="H88" s="22" t="s">
+      <c r="H88" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J88" s="58" t="s">
+      <c r="J88" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="K88" s="59">
+      <c r="K88" s="40">
         <f>AVERAGE(F41:F45)</f>
         <v>0.50519999999999998</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="J89" s="58" t="s">
+      <c r="J89" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="K89" s="60">
+      <c r="K89" s="41">
         <f>VARPA(E41:E45)*5</f>
         <v>6.7287015917140157E-6</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="J90" s="58" t="s">
+      <c r="J90" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="K90" s="60">
+      <c r="K90" s="41">
         <f>J76/I74*SQRT(1+1/5+((E70-K88)^2)/(I74^2*K89))</f>
         <v>4.6191380379766698E-5</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="23" t="s">
+      <c r="A91" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G91" s="27">
+      <c r="G91" s="18">
         <f>K91*K90</f>
         <v>1.4700158782554295E-4</v>
       </c>
-      <c r="H91" s="22" t="s">
+      <c r="H91" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J91" s="58" t="s">
+      <c r="J91" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="K91" s="59">
+      <c r="K91" s="40">
         <f>_xlfn.T.INV.2T(0.05,J77)</f>
         <v>3.1824463052837091</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="23"/>
+      <c r="A92" s="2"/>
     </row>
     <row r="93" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="94" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="23" t="s">
+      <c r="A94" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G94" s="29">
+      <c r="G94" s="20">
         <f>G88*25/E64*100</f>
         <v>5.3146964781024053</v>
       </c>
-      <c r="H94" s="30" t="s">
+      <c r="H94" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="I94" s="29">
+      <c r="I94" s="20">
         <f>G91*25/E64*100</f>
         <v>0.36750396956385739</v>
       </c>
-      <c r="J94" s="26" t="s">
+      <c r="J94" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="96" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="23"/>
+      <c r="A96" s="2"/>
     </row>
     <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="23" t="s">
+      <c r="A97" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="23"/>
+      <c r="A98" s="2"/>
     </row>
     <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="23"/>
-      <c r="B99" s="31"/>
-      <c r="C99" s="31"/>
-      <c r="D99" s="31"/>
-      <c r="E99" s="31"/>
-      <c r="F99" s="31"/>
-      <c r="G99" s="31"/>
-      <c r="H99" s="31"/>
-      <c r="I99" s="31"/>
-      <c r="J99" s="32"/>
+      <c r="A99" s="2"/>
+      <c r="B99" s="54"/>
+      <c r="C99" s="54"/>
+      <c r="D99" s="54"/>
+      <c r="E99" s="54"/>
+      <c r="F99" s="54"/>
+      <c r="G99" s="54"/>
+      <c r="H99" s="54"/>
+      <c r="I99" s="54"/>
+      <c r="J99" s="15"/>
     </row>
     <row r="100" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="23"/>
+      <c r="A100" s="2"/>
     </row>
     <row r="101" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="102" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="23" t="s">
+      <c r="A102" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B103" s="23" t="s">
+      <c r="B103" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C104" s="53" t="s">
+      <c r="C104" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D104" s="53" t="s">
+      <c r="D104" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="E104" s="53" t="s">
+      <c r="E104" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="F104" s="53" t="s">
+      <c r="F104" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="G104" s="53" t="s">
+      <c r="G104" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="H104" s="53" t="s">
+      <c r="H104" s="38" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C105" s="36" t="s">
+      <c r="C105" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D105" s="33">
+      <c r="D105" s="22">
         <f>G94</f>
         <v>5.3146964781024053</v>
       </c>
-      <c r="E105" s="33">
+      <c r="E105" s="22">
         <f>I94</f>
         <v>0.36750396956385739</v>
       </c>
-      <c r="F105" s="34">
+      <c r="F105" s="52">
         <f>AVERAGE(D105:D112)</f>
         <v>5.3146964781024053</v>
       </c>
-      <c r="G105" s="35" t="e">
+      <c r="G105" s="53" t="e">
         <f>STDEV(D105:D112)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H105" s="35" t="e">
+      <c r="H105" s="53" t="e">
         <f>G105/F105*100</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C106" s="36"/>
-      <c r="D106" s="33"/>
-      <c r="E106" s="33"/>
-      <c r="F106" s="34"/>
-      <c r="G106" s="35"/>
-      <c r="H106" s="35"/>
+      <c r="C106" s="23"/>
+      <c r="D106" s="22"/>
+      <c r="E106" s="22"/>
+      <c r="F106" s="52"/>
+      <c r="G106" s="53"/>
+      <c r="H106" s="53"/>
     </row>
     <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C107" s="36"/>
-      <c r="D107" s="33"/>
-      <c r="E107" s="33"/>
-      <c r="F107" s="34"/>
-      <c r="G107" s="35"/>
-      <c r="H107" s="35"/>
+      <c r="C107" s="23"/>
+      <c r="D107" s="22"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="52"/>
+      <c r="G107" s="53"/>
+      <c r="H107" s="53"/>
     </row>
     <row r="108" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C108" s="36"/>
-      <c r="D108" s="33"/>
-      <c r="E108" s="33"/>
-      <c r="F108" s="34"/>
-      <c r="G108" s="35"/>
-      <c r="H108" s="35"/>
+      <c r="C108" s="23"/>
+      <c r="D108" s="22"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="52"/>
+      <c r="G108" s="53"/>
+      <c r="H108" s="53"/>
     </row>
     <row r="109" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C109" s="36"/>
-      <c r="D109" s="36"/>
-      <c r="E109" s="36"/>
-      <c r="F109" s="34"/>
-      <c r="G109" s="35"/>
-      <c r="H109" s="35"/>
+      <c r="C109" s="23"/>
+      <c r="D109" s="23"/>
+      <c r="E109" s="23"/>
+      <c r="F109" s="52"/>
+      <c r="G109" s="53"/>
+      <c r="H109" s="53"/>
     </row>
     <row r="110" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C110" s="36"/>
-      <c r="D110" s="36"/>
-      <c r="E110" s="36"/>
-      <c r="F110" s="34"/>
-      <c r="G110" s="35"/>
-      <c r="H110" s="35"/>
+      <c r="C110" s="23"/>
+      <c r="D110" s="23"/>
+      <c r="E110" s="23"/>
+      <c r="F110" s="52"/>
+      <c r="G110" s="53"/>
+      <c r="H110" s="53"/>
     </row>
     <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="34"/>
-      <c r="G111" s="35"/>
-      <c r="H111" s="35"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="52"/>
+      <c r="G111" s="53"/>
+      <c r="H111" s="53"/>
     </row>
     <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C112" s="36"/>
-      <c r="D112" s="36"/>
-      <c r="E112" s="36"/>
-      <c r="F112" s="34"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-    </row>
-    <row r="114" spans="1:20" s="23" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="22"/>
-      <c r="B114" s="22"/>
-      <c r="C114" s="22"/>
-      <c r="D114" s="22"/>
-      <c r="E114" s="22"/>
-      <c r="F114" s="22"/>
-      <c r="G114" s="22"/>
-      <c r="H114" s="22"/>
-      <c r="I114" s="22"/>
-      <c r="J114" s="22"/>
-      <c r="K114" s="22"/>
-      <c r="L114" s="22"/>
-      <c r="M114" s="22"/>
-      <c r="N114" s="22"/>
-      <c r="O114" s="22"/>
-      <c r="P114" s="22"/>
-      <c r="Q114" s="22"/>
-      <c r="R114" s="22"/>
-      <c r="S114" s="22"/>
-      <c r="T114" s="22"/>
+      <c r="C112" s="23"/>
+      <c r="D112" s="23"/>
+      <c r="E112" s="23"/>
+      <c r="F112" s="52"/>
+      <c r="G112" s="53"/>
+      <c r="H112" s="53"/>
+    </row>
+    <row r="114" spans="1:20" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1"/>
+      <c r="N114" s="1"/>
+      <c r="O114" s="1"/>
+      <c r="P114" s="1"/>
+      <c r="Q114" s="1"/>
+      <c r="R114" s="1"/>
+      <c r="S114" s="1"/>
+      <c r="T114" s="1"/>
     </row>
     <row r="115" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="23" t="s">
+      <c r="A115" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B115" s="23"/>
-      <c r="C115" s="23"/>
-      <c r="D115" s="23"/>
-      <c r="E115" s="23"/>
-      <c r="F115" s="23"/>
-      <c r="G115" s="23"/>
-      <c r="H115" s="23"/>
-      <c r="I115" s="23"/>
-      <c r="J115" s="23"/>
-      <c r="K115" s="23"/>
-      <c r="L115" s="23"/>
-      <c r="M115" s="23"/>
-      <c r="N115" s="23"/>
-      <c r="O115" s="23"/>
-      <c r="P115" s="23"/>
-      <c r="Q115" s="23"/>
-      <c r="R115" s="23"/>
-      <c r="S115" s="23"/>
-      <c r="T115" s="23"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
+      <c r="M115" s="2"/>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" s="2"/>
+      <c r="Q115" s="2"/>
+      <c r="R115" s="2"/>
+      <c r="S115" s="2"/>
+      <c r="T115" s="2"/>
     </row>
     <row r="117" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B117" s="61"/>
-      <c r="C117" s="61"/>
-      <c r="D117" s="61"/>
-      <c r="E117" s="61"/>
-      <c r="F117" s="61"/>
-      <c r="G117" s="61"/>
-      <c r="H117" s="61"/>
+      <c r="B117" s="42"/>
+      <c r="C117" s="42"/>
+      <c r="D117" s="42"/>
+      <c r="E117" s="42"/>
+      <c r="F117" s="42"/>
+      <c r="G117" s="42"/>
+      <c r="H117" s="42"/>
     </row>
     <row r="118" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="61"/>
-      <c r="C118" s="61"/>
-      <c r="D118" s="61"/>
-      <c r="E118" s="61"/>
-      <c r="F118" s="61"/>
-      <c r="G118" s="61"/>
-      <c r="H118" s="61"/>
-      <c r="J118" s="37"/>
+      <c r="B118" s="42"/>
+      <c r="C118" s="42"/>
+      <c r="D118" s="42"/>
+      <c r="E118" s="42"/>
+      <c r="F118" s="42"/>
+      <c r="G118" s="42"/>
+      <c r="H118" s="42"/>
+      <c r="J118" s="24"/>
     </row>
     <row r="119" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B119" s="61"/>
-      <c r="C119" s="61"/>
-      <c r="D119" s="61"/>
-      <c r="E119" s="61"/>
-      <c r="F119" s="61"/>
-      <c r="G119" s="61"/>
-      <c r="H119" s="61"/>
+      <c r="B119" s="42"/>
+      <c r="C119" s="42"/>
+      <c r="D119" s="42"/>
+      <c r="E119" s="42"/>
+      <c r="F119" s="42"/>
+      <c r="G119" s="42"/>
+      <c r="H119" s="42"/>
     </row>
     <row r="120" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B120" s="61"/>
-      <c r="C120" s="61"/>
-      <c r="D120" s="61"/>
-      <c r="E120" s="61"/>
-      <c r="F120" s="61"/>
-      <c r="G120" s="61"/>
-      <c r="H120" s="61"/>
+      <c r="B120" s="42"/>
+      <c r="C120" s="42"/>
+      <c r="D120" s="42"/>
+      <c r="E120" s="42"/>
+      <c r="F120" s="42"/>
+      <c r="G120" s="42"/>
+      <c r="H120" s="42"/>
     </row>
     <row r="121" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B121" s="61"/>
-      <c r="C121" s="61"/>
-      <c r="D121" s="61"/>
-      <c r="E121" s="61"/>
-      <c r="F121" s="61"/>
-      <c r="G121" s="61"/>
-      <c r="H121" s="61"/>
+      <c r="B121" s="42"/>
+      <c r="C121" s="42"/>
+      <c r="D121" s="42"/>
+      <c r="E121" s="42"/>
+      <c r="F121" s="42"/>
+      <c r="G121" s="42"/>
+      <c r="H121" s="42"/>
     </row>
     <row r="122" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B122" s="61"/>
-      <c r="C122" s="61"/>
-      <c r="D122" s="61"/>
-      <c r="E122" s="61"/>
-      <c r="F122" s="61"/>
-      <c r="G122" s="61"/>
-      <c r="H122" s="61"/>
-    </row>
-    <row r="123" spans="1:20" s="38" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="22"/>
-      <c r="B123" s="22"/>
-      <c r="C123" s="22"/>
-      <c r="D123" s="22"/>
-      <c r="E123" s="22"/>
-      <c r="F123" s="22"/>
-      <c r="G123" s="22"/>
-      <c r="H123" s="22"/>
-      <c r="I123" s="22"/>
-      <c r="J123" s="22"/>
-      <c r="K123" s="22"/>
-      <c r="L123" s="22"/>
-      <c r="M123" s="22"/>
-      <c r="N123" s="22"/>
-      <c r="O123" s="22"/>
-      <c r="P123" s="22"/>
-      <c r="Q123" s="22"/>
-      <c r="R123" s="22"/>
-      <c r="S123" s="22"/>
-      <c r="T123" s="22"/>
-    </row>
-    <row r="124" spans="1:20" s="38" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B124" s="38" t="s">
+      <c r="B122" s="42"/>
+      <c r="C122" s="42"/>
+      <c r="D122" s="42"/>
+      <c r="E122" s="42"/>
+      <c r="F122" s="42"/>
+      <c r="G122" s="42"/>
+      <c r="H122" s="42"/>
+    </row>
+    <row r="123" spans="1:20" s="8" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
+      <c r="K123" s="1"/>
+      <c r="L123" s="1"/>
+      <c r="M123" s="1"/>
+      <c r="N123" s="1"/>
+      <c r="O123" s="1"/>
+      <c r="P123" s="1"/>
+      <c r="Q123" s="1"/>
+      <c r="R123" s="1"/>
+      <c r="S123" s="1"/>
+      <c r="T123" s="1"/>
+    </row>
+    <row r="124" spans="1:20" s="8" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B124" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="125" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A125" s="38"/>
-      <c r="B125" s="38" t="s">
+      <c r="A125" s="8"/>
+      <c r="B125" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C125" s="38"/>
-      <c r="D125" s="38"/>
-      <c r="E125" s="38"/>
-      <c r="F125" s="38"/>
-      <c r="G125" s="38"/>
-      <c r="H125" s="38"/>
-      <c r="I125" s="38"/>
-      <c r="J125" s="38"/>
-      <c r="K125" s="38"/>
-      <c r="L125" s="38"/>
-      <c r="M125" s="38"/>
-      <c r="N125" s="38"/>
-      <c r="O125" s="38"/>
-      <c r="P125" s="38"/>
-      <c r="Q125" s="38"/>
-      <c r="R125" s="38"/>
-      <c r="S125" s="38"/>
-      <c r="T125" s="38"/>
+      <c r="C125" s="8"/>
+      <c r="D125" s="8"/>
+      <c r="E125" s="8"/>
+      <c r="F125" s="8"/>
+      <c r="G125" s="8"/>
+      <c r="H125" s="8"/>
+      <c r="I125" s="8"/>
+      <c r="J125" s="8"/>
+      <c r="K125" s="8"/>
+      <c r="L125" s="8"/>
+      <c r="M125" s="8"/>
+      <c r="N125" s="8"/>
+      <c r="O125" s="8"/>
+      <c r="P125" s="8"/>
+      <c r="Q125" s="8"/>
+      <c r="R125" s="8"/>
+      <c r="S125" s="8"/>
+      <c r="T125" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7324,74 +7410,72 @@
     <col min="10" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="39">
+      <c r="F1" s="25">
         <v>45796</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="21" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="26" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
       <c r="E3"/>
       <c r="F3"/>
     </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" ht="207" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="14" t="s">
         <v>48</v>
       </c>
@@ -7401,23 +7485,24 @@
       <c r="E12" s="14" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G12" s="27"/>
+    </row>
+    <row r="13" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
     </row>
-    <row r="14" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
     </row>
-    <row r="15" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
     </row>
-    <row r="16" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -7532,65 +7617,65 @@
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="17"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="59"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="11"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="17"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="59"/>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="11"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="17"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="59"/>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="11"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="17"/>
+      <c r="F57" s="55"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="59"/>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="11"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="17"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="59"/>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="11"/>
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="17"/>
+      <c r="F59" s="55"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="59"/>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="11"/>
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="17"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="59"/>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C61" s="12"/>
       <c r="D61" s="10"/>
       <c r="E61" s="10"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="16"/>
-      <c r="H61" s="18"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="58"/>
+      <c r="H61" s="60"/>
     </row>
     <row r="62" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="63" spans="1:8" s="2" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.15">
@@ -7662,6 +7747,7 @@
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="83" fitToHeight="2" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
